--- a/Team-Data/2011-12/3-20-2011-12.xlsx
+++ b/Team-Data/2011-12/3-20-2011-12.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>1.9</v>
       </c>
       <c r="AD2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE2" t="n">
         <v>8</v>
@@ -781,22 +848,22 @@
         <v>25</v>
       </c>
       <c r="AR2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT2" t="n">
         <v>25</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>24</v>
       </c>
       <c r="AU2" t="n">
         <v>9</v>
       </c>
       <c r="AV2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX2" t="n">
         <v>20</v>
@@ -814,7 +881,7 @@
         <v>23</v>
       </c>
       <c r="BC2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-20-2011-12</t>
+          <t>2012-03-20</t>
         </is>
       </c>
     </row>
@@ -921,10 +988,10 @@
         <v>0.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="AE3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF3" t="n">
         <v>13</v>
@@ -945,7 +1012,7 @@
         <v>7</v>
       </c>
       <c r="AL3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM3" t="n">
         <v>23</v>
@@ -954,7 +1021,7 @@
         <v>8</v>
       </c>
       <c r="AO3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP3" t="n">
         <v>27</v>
@@ -966,7 +1033,7 @@
         <v>30</v>
       </c>
       <c r="AS3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT3" t="n">
         <v>30</v>
@@ -981,10 +1048,10 @@
         <v>21</v>
       </c>
       <c r="AX3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ3" t="n">
         <v>21</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-20-2011-12</t>
+          <t>2012-03-20</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-13.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE4" t="n">
         <v>30</v>
@@ -1157,7 +1224,7 @@
         <v>21</v>
       </c>
       <c r="AV4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW4" t="n">
         <v>29</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-20-2011-12</t>
+          <t>2012-03-20</t>
         </is>
       </c>
     </row>
@@ -1303,7 +1370,7 @@
         <v>5</v>
       </c>
       <c r="AJ5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK5" t="n">
         <v>5</v>
@@ -1312,7 +1379,7 @@
         <v>18</v>
       </c>
       <c r="AM5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AN5" t="n">
         <v>6</v>
@@ -1348,7 +1415,7 @@
         <v>4</v>
       </c>
       <c r="AY5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ5" t="n">
         <v>2</v>
@@ -1357,7 +1424,7 @@
         <v>28</v>
       </c>
       <c r="BB5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC5" t="n">
         <v>1</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-20-2011-12</t>
+          <t>2012-03-20</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>-4.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AE6" t="n">
         <v>23</v>
@@ -1491,31 +1558,31 @@
         <v>27</v>
       </c>
       <c r="AL6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AM6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AO6" t="n">
         <v>9</v>
       </c>
       <c r="AP6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AQ6" t="n">
         <v>28</v>
       </c>
       <c r="AR6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS6" t="n">
         <v>23</v>
       </c>
       <c r="AT6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU6" t="n">
         <v>19</v>
@@ -1542,7 +1609,7 @@
         <v>20</v>
       </c>
       <c r="BC6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-20-2011-12</t>
+          <t>2012-03-20</t>
         </is>
       </c>
     </row>
@@ -1658,7 +1725,7 @@
         <v>10</v>
       </c>
       <c r="AG7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH7" t="n">
         <v>19</v>
@@ -1670,22 +1737,22 @@
         <v>10</v>
       </c>
       <c r="AK7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL7" t="n">
         <v>6</v>
       </c>
       <c r="AM7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO7" t="n">
         <v>26</v>
       </c>
       <c r="AP7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ7" t="n">
         <v>14</v>
@@ -1721,7 +1788,7 @@
         <v>25</v>
       </c>
       <c r="BB7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BC7" t="n">
         <v>7</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-20-2011-12</t>
+          <t>2012-03-20</t>
         </is>
       </c>
     </row>
@@ -1831,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="AD8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF8" t="n">
         <v>13</v>
@@ -1849,19 +1916,19 @@
         <v>3</v>
       </c>
       <c r="AJ8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK8" t="n">
         <v>4</v>
       </c>
       <c r="AL8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AM8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AN8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO8" t="n">
         <v>2</v>
@@ -1873,13 +1940,13 @@
         <v>22</v>
       </c>
       <c r="AR8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS8" t="n">
         <v>5</v>
       </c>
       <c r="AT8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AU8" t="n">
         <v>1</v>
@@ -1891,7 +1958,7 @@
         <v>5</v>
       </c>
       <c r="AX8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY8" t="n">
         <v>30</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-20-2011-12</t>
+          <t>2012-03-20</t>
         </is>
       </c>
     </row>
@@ -2013,16 +2080,16 @@
         <v>-5.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="AE9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF9" t="n">
         <v>24</v>
       </c>
       <c r="AG9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH9" t="n">
         <v>15</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-20-2011-12</t>
+          <t>2012-03-20</t>
         </is>
       </c>
     </row>
@@ -2195,13 +2262,13 @@
         <v>-1.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AE10" t="n">
         <v>22</v>
       </c>
       <c r="AF10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG10" t="n">
         <v>22</v>
@@ -2213,7 +2280,7 @@
         <v>8</v>
       </c>
       <c r="AJ10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK10" t="n">
         <v>6</v>
@@ -2228,7 +2295,7 @@
         <v>3</v>
       </c>
       <c r="AO10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP10" t="n">
         <v>25</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-20-2011-12</t>
+          <t>2012-03-20</t>
         </is>
       </c>
     </row>
@@ -2299,25 +2366,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F11" t="n">
         <v>22</v>
       </c>
       <c r="G11" t="n">
-        <v>0.532</v>
+        <v>0.522</v>
       </c>
       <c r="H11" t="n">
         <v>48.5</v>
       </c>
       <c r="I11" t="n">
-        <v>37.6</v>
+        <v>37.5</v>
       </c>
       <c r="J11" t="n">
-        <v>82.8</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K11" t="n">
         <v>0.453</v>
@@ -2329,31 +2396,31 @@
         <v>19.4</v>
       </c>
       <c r="N11" t="n">
-        <v>0.36</v>
+        <v>0.358</v>
       </c>
       <c r="O11" t="n">
         <v>15.7</v>
       </c>
       <c r="P11" t="n">
-        <v>20.1</v>
+        <v>19.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.784</v>
+        <v>0.785</v>
       </c>
       <c r="R11" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="S11" t="n">
-        <v>30.3</v>
+        <v>30.5</v>
       </c>
       <c r="T11" t="n">
         <v>41.8</v>
       </c>
       <c r="U11" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="V11" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="W11" t="n">
         <v>7.3</v>
@@ -2371,16 +2438,16 @@
         <v>18.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>97.90000000000001</v>
+        <v>97.7</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AF11" t="n">
         <v>15</v>
@@ -2398,37 +2465,37 @@
         <v>6</v>
       </c>
       <c r="AK11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AL11" t="n">
         <v>11</v>
       </c>
-      <c r="AL11" t="n">
-        <v>10</v>
-      </c>
       <c r="AM11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ11" t="n">
         <v>4</v>
       </c>
       <c r="AR11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AS11" t="n">
         <v>17</v>
       </c>
       <c r="AT11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AV11" t="n">
         <v>16</v>
@@ -2443,7 +2510,7 @@
         <v>15</v>
       </c>
       <c r="AZ11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA11" t="n">
         <v>26</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-20-2011-12</t>
+          <t>2012-03-20</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F12" t="n">
         <v>18</v>
       </c>
       <c r="G12" t="n">
-        <v>0.591</v>
+        <v>0.581</v>
       </c>
       <c r="H12" t="n">
         <v>48.3</v>
@@ -2499,37 +2566,37 @@
         <v>34.8</v>
       </c>
       <c r="J12" t="n">
-        <v>80.7</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>0.432</v>
+        <v>0.431</v>
       </c>
       <c r="L12" t="n">
         <v>5.6</v>
       </c>
       <c r="M12" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="N12" t="n">
-        <v>0.363</v>
+        <v>0.358</v>
       </c>
       <c r="O12" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="P12" t="n">
         <v>26</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.776</v>
+        <v>0.773</v>
       </c>
       <c r="R12" t="n">
         <v>12.3</v>
       </c>
       <c r="S12" t="n">
-        <v>31.1</v>
+        <v>31.2</v>
       </c>
       <c r="T12" t="n">
-        <v>43.4</v>
+        <v>43.5</v>
       </c>
       <c r="U12" t="n">
         <v>18</v>
@@ -2538,10 +2605,10 @@
         <v>14.3</v>
       </c>
       <c r="W12" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="X12" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Y12" t="n">
         <v>6.1</v>
@@ -2553,25 +2620,25 @@
         <v>21.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>95.5</v>
+        <v>95.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AE12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG12" t="n">
         <v>8</v>
       </c>
-      <c r="AF12" t="n">
-        <v>5</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>7</v>
-      </c>
       <c r="AH12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI12" t="n">
         <v>25</v>
@@ -2583,13 +2650,13 @@
         <v>26</v>
       </c>
       <c r="AL12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM12" t="n">
         <v>22</v>
       </c>
       <c r="AN12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO12" t="n">
         <v>3</v>
@@ -2598,25 +2665,25 @@
         <v>3</v>
       </c>
       <c r="AQ12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AR12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS12" t="n">
         <v>12</v>
       </c>
       <c r="AT12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AU12" t="n">
         <v>30</v>
       </c>
       <c r="AV12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AW12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AX12" t="n">
         <v>11</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-20-2011-12</t>
+          <t>2012-03-20</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E13" t="n">
         <v>26</v>
       </c>
       <c r="F13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G13" t="n">
-        <v>0.578</v>
+        <v>0.591</v>
       </c>
       <c r="H13" t="n">
         <v>48.6</v>
@@ -2693,31 +2760,31 @@
         <v>21.4</v>
       </c>
       <c r="N13" t="n">
-        <v>0.351</v>
+        <v>0.353</v>
       </c>
       <c r="O13" t="n">
-        <v>16.3</v>
+        <v>16.5</v>
       </c>
       <c r="P13" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R13" t="n">
         <v>12.3</v>
       </c>
       <c r="S13" t="n">
-        <v>30.3</v>
+        <v>30.5</v>
       </c>
       <c r="T13" t="n">
-        <v>42.6</v>
+        <v>42.8</v>
       </c>
       <c r="U13" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="V13" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="W13" t="n">
         <v>8</v>
@@ -2726,31 +2793,31 @@
         <v>4.8</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>97.09999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AD13" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AE13" t="n">
         <v>8</v>
       </c>
       <c r="AF13" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AG13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH13" t="n">
         <v>5</v>
@@ -2759,7 +2826,7 @@
         <v>13</v>
       </c>
       <c r="AJ13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK13" t="n">
         <v>13</v>
@@ -2771,7 +2838,7 @@
         <v>5</v>
       </c>
       <c r="AN13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO13" t="n">
         <v>17</v>
@@ -2783,22 +2850,22 @@
         <v>29</v>
       </c>
       <c r="AR13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS13" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AT13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV13" t="n">
         <v>3</v>
       </c>
       <c r="AW13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX13" t="n">
         <v>19</v>
@@ -2813,10 +2880,10 @@
         <v>5</v>
       </c>
       <c r="BB13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-20-2011-12</t>
+          <t>2012-03-20</t>
         </is>
       </c>
     </row>
@@ -2845,28 +2912,28 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E14" t="n">
         <v>28</v>
       </c>
       <c r="F14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G14" t="n">
-        <v>0.609</v>
+        <v>0.622</v>
       </c>
       <c r="H14" t="n">
         <v>48.7</v>
       </c>
       <c r="I14" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="J14" t="n">
-        <v>79.3</v>
+        <v>79.2</v>
       </c>
       <c r="K14" t="n">
-        <v>0.454</v>
+        <v>0.453</v>
       </c>
       <c r="L14" t="n">
         <v>5.3</v>
@@ -2875,25 +2942,25 @@
         <v>17.2</v>
       </c>
       <c r="N14" t="n">
-        <v>0.308</v>
+        <v>0.306</v>
       </c>
       <c r="O14" t="n">
         <v>18.2</v>
       </c>
       <c r="P14" t="n">
-        <v>24.1</v>
+        <v>24.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.754</v>
+        <v>0.752</v>
       </c>
       <c r="R14" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="S14" t="n">
-        <v>34.1</v>
+        <v>34.4</v>
       </c>
       <c r="T14" t="n">
-        <v>45.5</v>
+        <v>45.8</v>
       </c>
       <c r="U14" t="n">
         <v>21.4</v>
@@ -2908,22 +2975,22 @@
         <v>5.4</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Z14" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="AA14" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AB14" t="n">
-        <v>95.40000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE14" t="n">
         <v>6</v>
@@ -2932,7 +2999,7 @@
         <v>5</v>
       </c>
       <c r="AG14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH14" t="n">
         <v>4</v>
@@ -2941,10 +3008,10 @@
         <v>18</v>
       </c>
       <c r="AJ14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AL14" t="n">
         <v>24</v>
@@ -2953,7 +3020,7 @@
         <v>18</v>
       </c>
       <c r="AN14" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO14" t="n">
         <v>8</v>
@@ -2962,10 +3029,10 @@
         <v>9</v>
       </c>
       <c r="AQ14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AS14" t="n">
         <v>1</v>
@@ -2992,7 +3059,7 @@
         <v>6</v>
       </c>
       <c r="BA14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB14" t="n">
         <v>17</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-20-2011-12</t>
+          <t>2012-03-20</t>
         </is>
       </c>
     </row>
@@ -3027,37 +3094,37 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E15" t="n">
         <v>25</v>
       </c>
       <c r="F15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.581</v>
       </c>
       <c r="H15" t="n">
         <v>48.5</v>
       </c>
       <c r="I15" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J15" t="n">
-        <v>82.5</v>
+        <v>82.3</v>
       </c>
       <c r="K15" t="n">
-        <v>0.449</v>
+        <v>0.448</v>
       </c>
       <c r="L15" t="n">
         <v>3.8</v>
       </c>
       <c r="M15" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="N15" t="n">
-        <v>0.319</v>
+        <v>0.321</v>
       </c>
       <c r="O15" t="n">
         <v>17.6</v>
@@ -3066,64 +3133,64 @@
         <v>23.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.752</v>
+        <v>0.75</v>
       </c>
       <c r="R15" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="S15" t="n">
-        <v>29.9</v>
+        <v>30</v>
       </c>
       <c r="T15" t="n">
-        <v>41.9</v>
+        <v>42</v>
       </c>
       <c r="U15" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="V15" t="n">
         <v>14.9</v>
       </c>
       <c r="W15" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="X15" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y15" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="Z15" t="n">
-        <v>20</v>
+        <v>19.8</v>
       </c>
       <c r="AA15" t="n">
         <v>20.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>95.40000000000001</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AD15" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AE15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI15" t="n">
         <v>12</v>
       </c>
-      <c r="AF15" t="n">
+      <c r="AJ15" t="n">
         <v>8</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>9</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>11</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>7</v>
       </c>
       <c r="AK15" t="n">
         <v>14</v>
@@ -3141,19 +3208,19 @@
         <v>11</v>
       </c>
       <c r="AP15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR15" t="n">
         <v>9</v>
       </c>
       <c r="AS15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU15" t="n">
         <v>23</v>
@@ -3171,16 +3238,16 @@
         <v>22</v>
       </c>
       <c r="AZ15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA15" t="n">
         <v>14</v>
       </c>
       <c r="BB15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-20-2011-12</t>
+          <t>2012-03-20</t>
         </is>
       </c>
     </row>
@@ -3209,55 +3276,55 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E16" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F16" t="n">
         <v>11</v>
       </c>
       <c r="G16" t="n">
-        <v>0.756</v>
+        <v>0.75</v>
       </c>
       <c r="H16" t="n">
         <v>48.8</v>
       </c>
       <c r="I16" t="n">
-        <v>38.2</v>
+        <v>38.3</v>
       </c>
       <c r="J16" t="n">
-        <v>79.3</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K16" t="n">
         <v>0.482</v>
       </c>
       <c r="L16" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="M16" t="n">
-        <v>14.7</v>
+        <v>14.9</v>
       </c>
       <c r="N16" t="n">
-        <v>0.388</v>
+        <v>0.391</v>
       </c>
       <c r="O16" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="P16" t="n">
-        <v>25.3</v>
+        <v>25.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.775</v>
+        <v>0.776</v>
       </c>
       <c r="R16" t="n">
         <v>10.2</v>
       </c>
       <c r="S16" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="T16" t="n">
-        <v>42.2</v>
+        <v>42.3</v>
       </c>
       <c r="U16" t="n">
         <v>21</v>
@@ -3266,37 +3333,37 @@
         <v>15</v>
       </c>
       <c r="W16" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="X16" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Y16" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z16" t="n">
         <v>20.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AB16" t="n">
         <v>101.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD16" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AE16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF16" t="n">
         <v>2</v>
       </c>
       <c r="AG16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH16" t="n">
         <v>2</v>
@@ -3326,10 +3393,10 @@
         <v>7</v>
       </c>
       <c r="AQ16" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AR16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS16" t="n">
         <v>8</v>
@@ -3353,7 +3420,7 @@
         <v>7</v>
       </c>
       <c r="AZ16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA16" t="n">
         <v>7</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-20-2011-12</t>
+          <t>2012-03-20</t>
         </is>
       </c>
     </row>
@@ -3391,100 +3458,100 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F17" t="n">
         <v>24</v>
       </c>
       <c r="G17" t="n">
-        <v>0.467</v>
+        <v>0.455</v>
       </c>
       <c r="H17" t="n">
         <v>48.1</v>
       </c>
       <c r="I17" t="n">
-        <v>37.2</v>
+        <v>36.9</v>
       </c>
       <c r="J17" t="n">
         <v>85.40000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>0.435</v>
+        <v>0.432</v>
       </c>
       <c r="L17" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="M17" t="n">
         <v>20.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0.344</v>
+        <v>0.339</v>
       </c>
       <c r="O17" t="n">
-        <v>16.7</v>
+        <v>16.9</v>
       </c>
       <c r="P17" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.795</v>
+        <v>0.796</v>
       </c>
       <c r="R17" t="n">
-        <v>12.8</v>
+        <v>13</v>
       </c>
       <c r="S17" t="n">
         <v>28.8</v>
       </c>
       <c r="T17" t="n">
-        <v>41.6</v>
+        <v>41.8</v>
       </c>
       <c r="U17" t="n">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="V17" t="n">
         <v>14.1</v>
       </c>
       <c r="W17" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X17" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y17" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Z17" t="n">
         <v>19.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>98</v>
+        <v>97.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.4</v>
+        <v>-1.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AE17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF17" t="n">
         <v>18</v>
       </c>
       <c r="AG17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH17" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AI17" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AJ17" t="n">
         <v>2</v>
@@ -3493,7 +3560,7 @@
         <v>25</v>
       </c>
       <c r="AL17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AM17" t="n">
         <v>12</v>
@@ -3502,7 +3569,7 @@
         <v>16</v>
       </c>
       <c r="AO17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP17" t="n">
         <v>22</v>
@@ -3511,13 +3578,13 @@
         <v>1</v>
       </c>
       <c r="AR17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS17" t="n">
         <v>28</v>
       </c>
       <c r="AT17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU17" t="n">
         <v>4</v>
@@ -3526,25 +3593,25 @@
         <v>7</v>
       </c>
       <c r="AW17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX17" t="n">
         <v>18</v>
       </c>
       <c r="AY17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ17" t="n">
         <v>14</v>
       </c>
       <c r="BA17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BB17" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="BC17" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-20-2011-12</t>
+          <t>2012-03-20</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3721,7 @@
         <v>2</v>
       </c>
       <c r="AE18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF18" t="n">
         <v>18</v>
@@ -3666,7 +3733,7 @@
         <v>24</v>
       </c>
       <c r="AI18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ18" t="n">
         <v>12</v>
@@ -3675,7 +3742,7 @@
         <v>24</v>
       </c>
       <c r="AL18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AM18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-20-2011-12</t>
+          <t>2012-03-20</t>
         </is>
       </c>
     </row>
@@ -3851,10 +3918,10 @@
         <v>29</v>
       </c>
       <c r="AJ19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL19" t="n">
         <v>3</v>
@@ -3872,7 +3939,7 @@
         <v>17</v>
       </c>
       <c r="AQ19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR19" t="n">
         <v>12</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-20-2011-12</t>
+          <t>2012-03-20</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-5</v>
       </c>
       <c r="AD20" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="AE20" t="n">
         <v>28</v>
@@ -4051,22 +4118,22 @@
         <v>28</v>
       </c>
       <c r="AP20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AQ20" t="n">
         <v>15</v>
       </c>
       <c r="AR20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS20" t="n">
         <v>25</v>
       </c>
       <c r="AT20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV20" t="n">
         <v>19</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-20-2011-12</t>
+          <t>2012-03-20</t>
         </is>
       </c>
     </row>
@@ -4119,64 +4186,64 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F21" t="n">
         <v>24</v>
       </c>
       <c r="G21" t="n">
-        <v>0.478</v>
+        <v>0.467</v>
       </c>
       <c r="H21" t="n">
         <v>48.3</v>
       </c>
       <c r="I21" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="J21" t="n">
         <v>81.2</v>
       </c>
       <c r="K21" t="n">
-        <v>0.44</v>
+        <v>0.439</v>
       </c>
       <c r="L21" t="n">
         <v>7.2</v>
       </c>
       <c r="M21" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="N21" t="n">
         <v>0.322</v>
       </c>
       <c r="O21" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="P21" t="n">
-        <v>25.8</v>
+        <v>25.6</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.749</v>
+        <v>0.75</v>
       </c>
       <c r="R21" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="S21" t="n">
         <v>30.7</v>
       </c>
       <c r="T21" t="n">
-        <v>42</v>
+        <v>41.9</v>
       </c>
       <c r="U21" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V21" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="W21" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="X21" t="n">
         <v>4.3</v>
@@ -4188,16 +4255,16 @@
         <v>21.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>97.90000000000001</v>
+        <v>97.8</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE21" t="n">
         <v>19</v>
@@ -4209,31 +4276,31 @@
         <v>19</v>
       </c>
       <c r="AH21" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AI21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ21" t="n">
         <v>18</v>
       </c>
       <c r="AK21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AM21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO21" t="n">
         <v>6</v>
       </c>
       <c r="AP21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ21" t="n">
         <v>20</v>
@@ -4245,7 +4312,7 @@
         <v>15</v>
       </c>
       <c r="AT21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU21" t="n">
         <v>22</v>
@@ -4269,10 +4336,10 @@
         <v>2</v>
       </c>
       <c r="BB21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC21" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-20-2011-12</t>
+          <t>2012-03-20</t>
         </is>
       </c>
     </row>
@@ -4301,28 +4368,28 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E22" t="n">
         <v>34</v>
       </c>
       <c r="F22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G22" t="n">
-        <v>0.739</v>
+        <v>0.756</v>
       </c>
       <c r="H22" t="n">
         <v>48.2</v>
       </c>
       <c r="I22" t="n">
-        <v>36.9</v>
+        <v>37</v>
       </c>
       <c r="J22" t="n">
-        <v>78.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="K22" t="n">
-        <v>0.472</v>
+        <v>0.473</v>
       </c>
       <c r="L22" t="n">
         <v>7.2</v>
@@ -4331,7 +4398,7 @@
         <v>20.4</v>
       </c>
       <c r="N22" t="n">
-        <v>0.354</v>
+        <v>0.353</v>
       </c>
       <c r="O22" t="n">
         <v>21.5</v>
@@ -4340,19 +4407,19 @@
         <v>27.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.792</v>
+        <v>0.793</v>
       </c>
       <c r="R22" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="S22" t="n">
-        <v>32.5</v>
+        <v>32.7</v>
       </c>
       <c r="T22" t="n">
         <v>43.3</v>
       </c>
       <c r="U22" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="V22" t="n">
         <v>16.6</v>
@@ -4361,40 +4428,40 @@
         <v>7.5</v>
       </c>
       <c r="X22" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z22" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AA22" t="n">
         <v>20.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>102.4</v>
+        <v>102.7</v>
       </c>
       <c r="AC22" t="n">
-        <v>5.8</v>
+        <v>6.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
       </c>
       <c r="AF22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH22" t="n">
         <v>21</v>
       </c>
       <c r="AI22" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AJ22" t="n">
         <v>28</v>
@@ -4403,13 +4470,13 @@
         <v>2</v>
       </c>
       <c r="AL22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AM22" t="n">
         <v>11</v>
       </c>
       <c r="AN22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO22" t="n">
         <v>1</v>
@@ -4430,7 +4497,7 @@
         <v>8</v>
       </c>
       <c r="AU22" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AV22" t="n">
         <v>30</v>
@@ -4442,10 +4509,10 @@
         <v>1</v>
       </c>
       <c r="AY22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ22" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BA22" t="n">
         <v>12</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-20-2011-12</t>
+          <t>2012-03-20</t>
         </is>
       </c>
     </row>
@@ -4567,10 +4634,10 @@
         <v>4</v>
       </c>
       <c r="AF23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH23" t="n">
         <v>12</v>
@@ -4603,10 +4670,10 @@
         <v>30</v>
       </c>
       <c r="AR23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT23" t="n">
         <v>11</v>
@@ -4636,7 +4703,7 @@
         <v>24</v>
       </c>
       <c r="BC23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-20-2011-12</t>
+          <t>2012-03-20</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>6.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE24" t="n">
         <v>8</v>
@@ -4755,7 +4822,7 @@
         <v>11</v>
       </c>
       <c r="AH24" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AI24" t="n">
         <v>6</v>
@@ -4767,7 +4834,7 @@
         <v>12</v>
       </c>
       <c r="AL24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM24" t="n">
         <v>24</v>
@@ -4785,7 +4852,7 @@
         <v>23</v>
       </c>
       <c r="AR24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS24" t="n">
         <v>2</v>
@@ -4800,7 +4867,7 @@
         <v>1</v>
       </c>
       <c r="AW24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX24" t="n">
         <v>17</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-20-2011-12</t>
+          <t>2012-03-20</t>
         </is>
       </c>
     </row>
@@ -4847,22 +4914,22 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E25" t="n">
         <v>23</v>
       </c>
       <c r="F25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5</v>
+        <v>0.511</v>
       </c>
       <c r="H25" t="n">
         <v>48</v>
       </c>
       <c r="I25" t="n">
-        <v>37</v>
+        <v>37.1</v>
       </c>
       <c r="J25" t="n">
         <v>81.7</v>
@@ -4874,25 +4941,25 @@
         <v>6.7</v>
       </c>
       <c r="M25" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="N25" t="n">
-        <v>0.347</v>
+        <v>0.346</v>
       </c>
       <c r="O25" t="n">
         <v>15.6</v>
       </c>
       <c r="P25" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.759</v>
+        <v>0.761</v>
       </c>
       <c r="R25" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="S25" t="n">
-        <v>31.2</v>
+        <v>31.3</v>
       </c>
       <c r="T25" t="n">
         <v>41.8</v>
@@ -4901,19 +4968,19 @@
         <v>22.7</v>
       </c>
       <c r="V25" t="n">
-        <v>14.4</v>
+        <v>14.2</v>
       </c>
       <c r="W25" t="n">
         <v>6.8</v>
       </c>
       <c r="X25" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Y25" t="n">
         <v>4.4</v>
       </c>
       <c r="Z25" t="n">
-        <v>18.6</v>
+        <v>18.4</v>
       </c>
       <c r="AA25" t="n">
         <v>19.2</v>
@@ -4925,28 +4992,28 @@
         <v>-0.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF25" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AG25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH25" t="n">
         <v>29</v>
       </c>
       <c r="AI25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ25" t="n">
         <v>13</v>
       </c>
       <c r="AK25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL25" t="n">
         <v>14</v>
@@ -4958,16 +5025,16 @@
         <v>15</v>
       </c>
       <c r="AO25" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AP25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ25" t="n">
         <v>13</v>
       </c>
       <c r="AR25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS25" t="n">
         <v>11</v>
@@ -4979,7 +5046,7 @@
         <v>5</v>
       </c>
       <c r="AV25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AW25" t="n">
         <v>26</v>
@@ -5000,7 +5067,7 @@
         <v>15</v>
       </c>
       <c r="BC25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-20-2011-12</t>
+          <t>2012-03-20</t>
         </is>
       </c>
     </row>
@@ -5029,100 +5096,100 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E26" t="n">
         <v>21</v>
       </c>
       <c r="F26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G26" t="n">
-        <v>0.457</v>
+        <v>0.467</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>36.4</v>
+        <v>36.6</v>
       </c>
       <c r="J26" t="n">
         <v>81.90000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>0.445</v>
+        <v>0.447</v>
       </c>
       <c r="L26" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="M26" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="N26" t="n">
-        <v>0.333</v>
+        <v>0.334</v>
       </c>
       <c r="O26" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="P26" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.789</v>
+        <v>0.788</v>
       </c>
       <c r="R26" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="S26" t="n">
-        <v>30.3</v>
+        <v>30.4</v>
       </c>
       <c r="T26" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="U26" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="V26" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="W26" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="X26" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Y26" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z26" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AA26" t="n">
         <v>20.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>96.90000000000001</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="AC26" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="AD26" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF26" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AG26" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AH26" t="n">
         <v>10</v>
       </c>
       <c r="AI26" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AJ26" t="n">
         <v>11</v>
@@ -5137,7 +5204,7 @@
         <v>13</v>
       </c>
       <c r="AN26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO26" t="n">
         <v>12</v>
@@ -5149,41 +5216,41 @@
         <v>3</v>
       </c>
       <c r="AR26" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>23</v>
+      </c>
+      <c r="AU26" t="n">
         <v>17</v>
       </c>
-      <c r="AS26" t="n">
-        <v>19</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>22</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>18</v>
-      </c>
       <c r="AV26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW26" t="n">
         <v>9</v>
       </c>
       <c r="AX26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC26" t="n">
         <v>14</v>
       </c>
-      <c r="AY26" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>11</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>14</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>15</v>
-      </c>
       <c r="BD26" t="n">
         <v>10</v>
       </c>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-20-2011-12</t>
+          <t>2012-03-20</t>
         </is>
       </c>
     </row>
@@ -5211,61 +5278,61 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F27" t="n">
         <v>29</v>
       </c>
       <c r="G27" t="n">
-        <v>0.37</v>
+        <v>0.356</v>
       </c>
       <c r="H27" t="n">
         <v>48.2</v>
       </c>
       <c r="I27" t="n">
-        <v>36.6</v>
+        <v>36.4</v>
       </c>
       <c r="J27" t="n">
-        <v>85.7</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>0.427</v>
+        <v>0.425</v>
       </c>
       <c r="L27" t="n">
         <v>6.6</v>
       </c>
       <c r="M27" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="N27" t="n">
-        <v>0.321</v>
+        <v>0.322</v>
       </c>
       <c r="O27" t="n">
         <v>17.7</v>
       </c>
       <c r="P27" t="n">
-        <v>23.6</v>
+        <v>23.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.753</v>
+        <v>0.756</v>
       </c>
       <c r="R27" t="n">
         <v>13.4</v>
       </c>
       <c r="S27" t="n">
-        <v>29.7</v>
+        <v>29.6</v>
       </c>
       <c r="T27" t="n">
-        <v>43.1</v>
+        <v>43</v>
       </c>
       <c r="U27" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="V27" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W27" t="n">
         <v>8.199999999999999</v>
@@ -5274,25 +5341,25 @@
         <v>4.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="Z27" t="n">
         <v>19.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AB27" t="n">
-        <v>97.5</v>
+        <v>97</v>
       </c>
       <c r="AC27" t="n">
-        <v>-5.7</v>
+        <v>-6</v>
       </c>
       <c r="AD27" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AF27" t="n">
         <v>24</v>
@@ -5304,31 +5371,31 @@
         <v>21</v>
       </c>
       <c r="AI27" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AJ27" t="n">
         <v>1</v>
       </c>
       <c r="AK27" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL27" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AM27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AN27" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AO27" t="n">
         <v>10</v>
       </c>
       <c r="AP27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR27" t="n">
         <v>2</v>
@@ -5337,16 +5404,16 @@
         <v>26</v>
       </c>
       <c r="AT27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU27" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AV27" t="n">
         <v>14</v>
       </c>
       <c r="AW27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX27" t="n">
         <v>23</v>
@@ -5361,7 +5428,7 @@
         <v>13</v>
       </c>
       <c r="BB27" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BC27" t="n">
         <v>27</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-20-2011-12</t>
+          <t>2012-03-20</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>4</v>
       </c>
       <c r="AD28" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AE28" t="n">
         <v>4</v>
@@ -5504,7 +5571,7 @@
         <v>1</v>
       </c>
       <c r="AO28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP28" t="n">
         <v>18</v>
@@ -5519,7 +5586,7 @@
         <v>10</v>
       </c>
       <c r="AT28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU28" t="n">
         <v>6</v>
@@ -5540,7 +5607,7 @@
         <v>1</v>
       </c>
       <c r="BA28" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB28" t="n">
         <v>4</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-20-2011-12</t>
+          <t>2012-03-20</t>
         </is>
       </c>
     </row>
@@ -5575,58 +5642,58 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E29" t="n">
         <v>15</v>
       </c>
       <c r="F29" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G29" t="n">
-        <v>0.326</v>
+        <v>0.333</v>
       </c>
       <c r="H29" t="n">
         <v>48.4</v>
       </c>
       <c r="I29" t="n">
-        <v>34.3</v>
+        <v>34.4</v>
       </c>
       <c r="J29" t="n">
-        <v>78.09999999999999</v>
+        <v>78.3</v>
       </c>
       <c r="K29" t="n">
-        <v>0.44</v>
+        <v>0.439</v>
       </c>
       <c r="L29" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="M29" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="N29" t="n">
-        <v>0.333</v>
+        <v>0.336</v>
       </c>
       <c r="O29" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="P29" t="n">
         <v>21.8</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.766</v>
+        <v>0.764</v>
       </c>
       <c r="R29" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="S29" t="n">
-        <v>30.9</v>
+        <v>31</v>
       </c>
       <c r="T29" t="n">
-        <v>41.1</v>
+        <v>41.4</v>
       </c>
       <c r="U29" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="V29" t="n">
         <v>15.4</v>
@@ -5635,7 +5702,7 @@
         <v>7</v>
       </c>
       <c r="X29" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Y29" t="n">
         <v>4.8</v>
@@ -5644,16 +5711,16 @@
         <v>24.4</v>
       </c>
       <c r="AA29" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="AB29" t="n">
-        <v>90.90000000000001</v>
+        <v>91</v>
       </c>
       <c r="AC29" t="n">
-        <v>-4.1</v>
+        <v>-3.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE29" t="n">
         <v>26</v>
@@ -5677,16 +5744,16 @@
         <v>21</v>
       </c>
       <c r="AL29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AN29" t="n">
         <v>18</v>
       </c>
       <c r="AO29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP29" t="n">
         <v>20</v>
@@ -5695,16 +5762,16 @@
         <v>11</v>
       </c>
       <c r="AR29" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AS29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT29" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AU29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AV29" t="n">
         <v>23</v>
@@ -5716,19 +5783,19 @@
         <v>16</v>
       </c>
       <c r="AY29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ29" t="n">
         <v>30</v>
       </c>
       <c r="BA29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB29" t="n">
         <v>27</v>
       </c>
       <c r="BC29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-20-2011-12</t>
+          <t>2012-03-20</t>
         </is>
       </c>
     </row>
@@ -5757,19 +5824,19 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F30" t="n">
         <v>22</v>
       </c>
       <c r="G30" t="n">
-        <v>0.522</v>
+        <v>0.511</v>
       </c>
       <c r="H30" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I30" t="n">
         <v>37.8</v>
@@ -5778,7 +5845,7 @@
         <v>83.3</v>
       </c>
       <c r="K30" t="n">
-        <v>0.455</v>
+        <v>0.454</v>
       </c>
       <c r="L30" t="n">
         <v>3.7</v>
@@ -5787,19 +5854,19 @@
         <v>12</v>
       </c>
       <c r="N30" t="n">
-        <v>0.308</v>
+        <v>0.304</v>
       </c>
       <c r="O30" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="P30" t="n">
         <v>24.4</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.751</v>
+        <v>0.752</v>
       </c>
       <c r="R30" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="S30" t="n">
         <v>30.3</v>
@@ -5817,28 +5884,28 @@
         <v>8.5</v>
       </c>
       <c r="X30" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Y30" t="n">
         <v>5.9</v>
       </c>
       <c r="Z30" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="AA30" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AB30" t="n">
         <v>97.7</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF30" t="n">
         <v>15</v>
@@ -5865,7 +5932,7 @@
         <v>29</v>
       </c>
       <c r="AN30" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AO30" t="n">
         <v>7</v>
@@ -5874,22 +5941,22 @@
         <v>8</v>
       </c>
       <c r="AQ30" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR30" t="n">
         <v>5</v>
       </c>
       <c r="AS30" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AT30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AU30" t="n">
         <v>12</v>
       </c>
       <c r="AV30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW30" t="n">
         <v>6</v>
@@ -5904,13 +5971,13 @@
         <v>29</v>
       </c>
       <c r="BA30" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BB30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BC30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-20-2011-12</t>
+          <t>2012-03-20</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="AD31" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
@@ -6047,7 +6114,7 @@
         <v>21</v>
       </c>
       <c r="AN31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO31" t="n">
         <v>19</v>
@@ -6065,7 +6132,7 @@
         <v>24</v>
       </c>
       <c r="AT31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU31" t="n">
         <v>28</v>
@@ -6074,7 +6141,7 @@
         <v>24</v>
       </c>
       <c r="AW31" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AX31" t="n">
         <v>2</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-20-2011-12</t>
+          <t>2012-03-20</t>
         </is>
       </c>
     </row>
